--- a/MDM4U Culminating Project “BATT”.xlsx
+++ b/MDM4U Culminating Project “BATT”.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="WinLossRateAndEV" sheetId="1" state="visible" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
   <si>
     <t xml:space="preserve">Win Rate Chart</t>
   </si>
@@ -93,8 +93,22 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">N/A
-You can not join the next round if you loss the previous round.</t>
+    <t xml:space="preserve">Win in R1 and Loss in R2 = 25% * 50% = 12.5% </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25% * 69.23% = 17.31%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25% * 30.77% = 7.69%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Win in R1 and R2, Loss in R3 = 25% * (4/13 * ¾ + 9/13 * 8/9) = 21.15%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25% * 30.77% * ¾ = 5.77%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25% * 69.23% * 8/9 = 15.38%</t>
   </si>
   <si>
     <t xml:space="preserve">Expected Value (if the initial coin in each round is 10 coin)</t>
@@ -260,7 +274,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -281,10 +295,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14.000000"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
+      <sz val="12.000000"/>
+      <color indexed="64"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
@@ -296,18 +309,12 @@
     <font>
       <sz val="16.000000"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16.000000"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -325,7 +332,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="12">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -333,18 +340,156 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="none"/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="38">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="9" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="16" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="10" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="9" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="16" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="10" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -352,15 +497,24 @@
       <alignment horizontal="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf fontId="3" fillId="0" borderId="9" numFmtId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf fontId="3" fillId="0" borderId="10" numFmtId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="11" numFmtId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="9" numFmtId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -375,33 +529,16 @@
     <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="6" fillId="0" borderId="0" numFmtId="9" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf fontId="6" fillId="0" borderId="0" numFmtId="10" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="7" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="7" fillId="0" borderId="0" numFmtId="9" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf fontId="7" fillId="0" borderId="0" numFmtId="10" xfId="0" applyNumberFormat="1" applyFont="1"/>
+      <alignment wrapText="1"/>
+    </xf>
     <xf fontId="7" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="8" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
       <protection hidden="0" locked="1"/>
     </xf>
@@ -922,340 +1059,356 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="3"/>
     </row>
     <row r="2" ht="14.25">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" ht="14.25">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="7">
         <v>0.25</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="8">
         <v>0.25</v>
       </c>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
+      <c r="C4"/>
+      <c r="D4" s="6"/>
     </row>
     <row r="5" ht="14.25">
-      <c r="A5" t="s">
+      <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="10">
         <v>0.30769999999999997</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" ht="14.25">
-      <c r="A6" t="s">
+      <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="10">
         <v>0.69230000000000003</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" ht="14.25">
-      <c r="A7" t="s">
+      <c r="A7" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
       </c>
+      <c r="C7"/>
+      <c r="D7" s="6"/>
     </row>
     <row r="8" ht="14.25">
-      <c r="A8" t="s">
+      <c r="A8" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="7">
         <v>0.25</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="6" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="9" ht="14.25">
-      <c r="A9" t="s">
+      <c r="A9" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="13">
         <v>0.11109999999999999</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="14" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="12" ht="21">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
     </row>
     <row r="13" ht="14.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="16" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" ht="14.25">
-      <c r="A14" s="5" t="s">
+    <row r="14" ht="15">
+      <c r="A14" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="7">
         <v>0.75</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="18">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="15" ht="45">
+      <c r="A15" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="19"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="20" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" ht="14.25">
-      <c r="A15" s="5" t="s">
+    <row r="16" ht="30">
+      <c r="A16" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="19"/>
+      <c r="C16" s="10">
+        <v>0.69230000000000003</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" ht="30">
+      <c r="A17" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="19"/>
+      <c r="C17" s="10">
+        <v>0.30769999999999997</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="A18" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="19"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" ht="60">
+      <c r="A19" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="19"/>
+      <c r="C19" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" ht="30">
+      <c r="A20" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="19"/>
+      <c r="C20" s="10">
+        <v>0.88879999999999992</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" ht="30"/>
+    <row r="23" ht="21">
+      <c r="A23" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+    </row>
+    <row r="24" ht="14.25">
+      <c r="A24" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="24"/>
+      <c r="D24" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" s="25" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25">
+      <c r="A25" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="26"/>
+      <c r="D25" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25">
+      <c r="A26" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="9"/>
-    </row>
-    <row r="16" ht="14.25">
-      <c r="A16" s="5" t="s">
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="28"/>
+    </row>
+    <row r="27" ht="14.25">
+      <c r="A27" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="4">
-        <v>0.69230000000000003</v>
-      </c>
-      <c r="D16" s="9"/>
-    </row>
-    <row r="17" ht="14.25">
-      <c r="A17" s="5" t="s">
+      <c r="B27" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="26"/>
+      <c r="D27" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="E27" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25">
+      <c r="A28" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="4">
-        <v>0.30769999999999997</v>
-      </c>
-      <c r="D17" s="9"/>
-    </row>
-    <row r="18" ht="14.25">
-      <c r="A18" s="5" t="s">
+      <c r="B28" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="26"/>
+      <c r="D28" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" s="28" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25">
+      <c r="A29" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="9"/>
-    </row>
-    <row r="19" ht="14.25">
-      <c r="A19" s="5" t="s">
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="28"/>
+    </row>
+    <row r="30" ht="14.25">
+      <c r="A30" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="D19" s="9"/>
-    </row>
-    <row r="20" ht="14.25">
-      <c r="A20" s="5" t="s">
+      <c r="B30" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="26"/>
+      <c r="D30" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="E30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25">
+      <c r="A31" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="4">
-        <v>0.88879999999999992</v>
-      </c>
-      <c r="D20" s="9"/>
-    </row>
-    <row r="23" ht="21">
-      <c r="A23" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-    </row>
-    <row r="24" ht="14.25">
-      <c r="A24" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25">
-      <c r="A25" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="E25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" ht="14.25">
-      <c r="A26" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="14"/>
-    </row>
-    <row r="27" ht="14.25">
-      <c r="A27" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="12"/>
-      <c r="D27" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="E27" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" ht="14.25">
-      <c r="A28" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="12"/>
-      <c r="D28" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="E28" s="14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="29" ht="14.25">
-      <c r="A29" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="14"/>
-    </row>
-    <row r="30" ht="14.25">
-      <c r="A30" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E30" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="31" ht="14.25">
-      <c r="A31" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C31" s="12"/>
-      <c r="D31" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>37</v>
+      <c r="B31" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" s="26"/>
+      <c r="D31" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="E31" s="28" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="32" ht="14.25">
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
+      <c r="B32" s="26"/>
+      <c r="C32" s="26"/>
     </row>
     <row r="33" ht="14.25">
-      <c r="A33" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>41</v>
+      <c r="A33" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" s="25" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="14">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="B14:B20"/>
-    <mergeCell ref="D14:D20"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>
@@ -1277,7 +1430,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="33.00390625"/>
     <col customWidth="1" min="2" max="2" width="25.140625"/>
@@ -1292,289 +1445,289 @@
   </cols>
   <sheetData>
     <row r="1" ht="21">
-      <c r="A1" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
+      <c r="A1" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
     </row>
     <row r="2">
-      <c r="A2" s="5"/>
-      <c r="B2" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>44</v>
+      <c r="A2" s="16"/>
+      <c r="B2" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="18">
+      <c r="A3" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="31">
         <v>0.75</v>
       </c>
-      <c r="D3" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="19">
+      <c r="D3" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="32">
         <v>0.74980000000000002</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" s="19">
+      <c r="A4" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="32">
         <v>0.69230000000000003</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5" s="17" t="s">
+      <c r="A5" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="32">
+        <v>0.30769999999999997</v>
+      </c>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+    </row>
+    <row r="6" ht="43" customHeight="1">
+      <c r="A6" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="32">
+        <v>0.125</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="32">
+        <v>0.12540000000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="19">
-        <v>0.30769999999999997</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-    </row>
-    <row r="6" ht="43" customHeight="1">
-      <c r="A6" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="19">
-        <v>0.125</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="19">
-        <v>0.12540000000000001</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="18">
+      <c r="C7" s="31">
         <v>0.75</v>
       </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="19">
+      <c r="A8" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="32">
         <v>0.88890000000000002</v>
       </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="19">
+      <c r="A9" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="32">
         <v>0.10580000000000001</v>
       </c>
-      <c r="D9" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="E9" s="19">
+      <c r="D9" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="32">
         <v>0.10580000000000001</v>
       </c>
     </row>
     <row r="10" ht="34.5" customHeight="1">
-      <c r="A10" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
+      <c r="A10" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
     </row>
     <row r="11" ht="21">
-      <c r="H11" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
+      <c r="H11" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29"/>
     </row>
     <row r="12">
-      <c r="I12" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="J12" s="23"/>
-      <c r="K12" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="L12" s="24"/>
+      <c r="I12" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="J12" s="24"/>
+      <c r="K12" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="L12" s="26"/>
     </row>
     <row r="13">
       <c r="H13" t="s">
-        <v>65</v>
-      </c>
-      <c r="I13" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="J13" s="25"/>
-      <c r="K13" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="L13" s="26"/>
+        <v>70</v>
+      </c>
+      <c r="I13" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="J13" s="35"/>
+      <c r="K13" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="L13" s="24"/>
     </row>
     <row r="14">
       <c r="H14" t="s">
-        <v>67</v>
-      </c>
-      <c r="I14" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="J14" s="25"/>
-      <c r="K14" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="L14" s="26"/>
+        <v>72</v>
+      </c>
+      <c r="I14" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="J14" s="35"/>
+      <c r="K14" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="L14" s="24"/>
     </row>
     <row r="15">
       <c r="H15" t="s">
-        <v>68</v>
-      </c>
-      <c r="I15" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="J15" s="25"/>
-      <c r="K15" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="L15" s="26"/>
+        <v>73</v>
+      </c>
+      <c r="I15" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="J15" s="35"/>
+      <c r="K15" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="L15" s="24"/>
     </row>
     <row r="16">
       <c r="H16" t="s">
-        <v>69</v>
-      </c>
-      <c r="I16" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="J16" s="25"/>
-      <c r="K16" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="L16" s="26"/>
+        <v>74</v>
+      </c>
+      <c r="I16" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="J16" s="35"/>
+      <c r="K16" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="L16" s="24"/>
     </row>
     <row r="17">
       <c r="H17" t="s">
-        <v>70</v>
-      </c>
-      <c r="I17" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="J17" s="25"/>
-      <c r="K17" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="L17" s="26"/>
+        <v>75</v>
+      </c>
+      <c r="I17" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="J17" s="35"/>
+      <c r="K17" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="L17" s="24"/>
     </row>
     <row r="18">
-      <c r="H18" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="I18" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="J18" s="28"/>
-      <c r="K18" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="L18" s="28"/>
+      <c r="H18" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="I18" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="J18" s="37"/>
+      <c r="K18" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="L18" s="37"/>
     </row>
     <row r="19">
-      <c r="H19" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="28"/>
+      <c r="H19" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="I19" s="37"/>
+      <c r="J19" s="37"/>
+      <c r="K19" s="37"/>
+      <c r="L19" s="37"/>
     </row>
     <row r="20">
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
+      <c r="H20" s="37"/>
+      <c r="I20" s="37"/>
+      <c r="J20" s="37"/>
+      <c r="K20" s="37"/>
+      <c r="L20" s="37"/>
     </row>
     <row r="21">
-      <c r="H21" s="28"/>
-      <c r="I21" s="28"/>
-      <c r="J21" s="28"/>
-      <c r="K21" s="28"/>
-      <c r="L21" s="28"/>
+      <c r="H21" s="37"/>
+      <c r="I21" s="37"/>
+      <c r="J21" s="37"/>
+      <c r="K21" s="37"/>
+      <c r="L21" s="37"/>
     </row>
     <row r="22">
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="28"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="28"/>
+      <c r="H22" s="37"/>
+      <c r="I22" s="37"/>
+      <c r="J22" s="37"/>
+      <c r="K22" s="37"/>
+      <c r="L22" s="37"/>
     </row>
     <row r="23">
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
+      <c r="L23" s="37"/>
     </row>
     <row r="24">
-      <c r="H24" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="I24" s="24"/>
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
+      <c r="H24" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="26"/>
     </row>
     <row r="25">
-      <c r="M25" s="5"/>
+      <c r="M25" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="20">
